--- a/docs/Mapping_casi_uso/cittadinanza/Citt_027.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_027.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="145">
   <si>
     <t>Sezione</t>
   </si>
@@ -276,6 +276,12 @@
   </si>
   <si>
     <t>nomeComuneAIRE</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>flag dichiarante</t>
@@ -499,11 +505,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.59765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="43.9609375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="25.734375" customWidth="true" bestFit="true"/>
@@ -1370,7 +1376,7 @@
         <v>88</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>34</v>
@@ -1433,53 +1439,53 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="F41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E42" s="2" t="s">
+      <c r="F42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>101</v>
@@ -1488,7 +1494,7 @@
         <v>33</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>102</v>
@@ -1497,12 +1503,12 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>103</v>
@@ -1511,7 +1517,7 @@
         <v>33</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>104</v>
@@ -1520,12 +1526,12 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>105</v>
@@ -1534,7 +1540,7 @@
         <v>33</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>106</v>
@@ -1543,12 +1549,12 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>107</v>
@@ -1557,44 +1563,44 @@
         <v>33</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>110</v>
@@ -1603,44 +1609,44 @@
         <v>33</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>113</v>
@@ -1649,7 +1655,7 @@
         <v>33</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>114</v>
@@ -1658,12 +1664,12 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>115</v>
@@ -1672,7 +1678,7 @@
         <v>33</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>116</v>
@@ -1681,12 +1687,12 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>117</v>
@@ -1695,7 +1701,7 @@
         <v>33</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>118</v>
@@ -1704,44 +1710,44 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>124</v>
@@ -1755,7 +1761,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>125</v>
@@ -1764,7 +1770,7 @@
         <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>126</v>
@@ -1778,7 +1784,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>127</v>
@@ -1787,7 +1793,7 @@
         <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>128</v>
@@ -1801,7 +1807,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>129</v>
@@ -1810,7 +1816,7 @@
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>130</v>
@@ -1824,16 +1830,16 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>132</v>
@@ -1847,7 +1853,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>133</v>
@@ -1856,7 +1862,7 @@
         <v>33</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>134</v>
@@ -1870,7 +1876,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>135</v>
@@ -1879,7 +1885,7 @@
         <v>33</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>136</v>
@@ -1893,7 +1899,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>137</v>
@@ -1902,7 +1908,7 @@
         <v>33</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>138</v>
@@ -1916,7 +1922,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>139</v>
@@ -1925,7 +1931,7 @@
         <v>33</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>140</v>
@@ -1939,7 +1945,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>141</v>
@@ -1948,7 +1954,7 @@
         <v>33</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>142</v>
@@ -1957,6 +1963,29 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G64" s="2" t="s">
         <v>18</v>
       </c>
     </row>
